--- a/80_Asset/画像リソース/入力設定.xlsx
+++ b/80_Asset/画像リソース/入力設定.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\画像リソース\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319527FC-3277-41F8-ABFE-2F8F2E016DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF01ACD8-C1FD-4F63-BC13-A5C50E4A86E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18720" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="30220" windowHeight="20220" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,8 +259,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7426411" y="1564055"/>
-          <a:ext cx="642984" cy="266430"/>
+          <a:off x="7445343" y="1530925"/>
+          <a:ext cx="644562" cy="260908"/>
           <a:chOff x="3673929" y="930729"/>
           <a:chExt cx="5154385" cy="549729"/>
         </a:xfrm>
@@ -446,8 +446,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4362828" y="1564055"/>
-          <a:ext cx="608469" cy="266430"/>
+          <a:off x="4373871" y="1530925"/>
+          <a:ext cx="610046" cy="260908"/>
           <a:chOff x="3673929" y="930729"/>
           <a:chExt cx="5154385" cy="549729"/>
         </a:xfrm>
@@ -633,8 +633,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5214733" y="1063724"/>
-          <a:ext cx="545940" cy="349525"/>
+          <a:off x="5228142" y="1041637"/>
+          <a:ext cx="547518" cy="338482"/>
           <a:chOff x="5246916" y="1072243"/>
           <a:chExt cx="549727" cy="353785"/>
         </a:xfrm>
@@ -778,8 +778,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6729264" y="1063724"/>
-          <a:ext cx="545941" cy="349525"/>
+          <a:off x="6746618" y="1041637"/>
+          <a:ext cx="547519" cy="338482"/>
           <a:chOff x="6770914" y="1072243"/>
           <a:chExt cx="549727" cy="353785"/>
         </a:xfrm>
@@ -923,8 +923,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3634882" y="1625520"/>
-          <a:ext cx="5149416" cy="1853176"/>
+          <a:off x="3644348" y="1586040"/>
+          <a:ext cx="5162826" cy="1809830"/>
           <a:chOff x="3657600" y="1638299"/>
           <a:chExt cx="5181600" cy="1872344"/>
         </a:xfrm>
@@ -1095,8 +1095,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3651211" y="605340"/>
-          <a:ext cx="5124094" cy="603211"/>
+          <a:off x="3660677" y="594297"/>
+          <a:ext cx="5136715" cy="586646"/>
           <a:chOff x="3673929" y="930729"/>
           <a:chExt cx="5154385" cy="549729"/>
         </a:xfrm>
@@ -2716,8 +2716,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4110707" y="1947415"/>
-          <a:ext cx="906208" cy="904207"/>
+          <a:off x="4120961" y="1903241"/>
+          <a:ext cx="908574" cy="882120"/>
           <a:chOff x="1738784" y="1871506"/>
           <a:chExt cx="914400" cy="914400"/>
         </a:xfrm>
@@ -4244,7 +4244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C846673B-40C5-4EBD-8ABB-1874D82E9909}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultColWidth="4" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="16384" width="4" style="1"/>
   </cols>

--- a/80_Asset/画像リソース/入力設定.xlsx
+++ b/80_Asset/画像リソース/入力設定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\画像リソース\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA31532-F433-4E65-8F83-316DEC04731E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151C90C4-48B9-4E36-825D-7DCFE0435E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7491" yWindow="4877" windowWidth="24686" windowHeight="13637" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
   </bookViews>
@@ -5742,7 +5742,7 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>205273</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2290371" cy="328423"/>
+    <xdr:ext cx="2149306" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="39" name="テキスト ボックス 38">
@@ -5757,7 +5757,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1187499" y="4894504"/>
-          <a:ext cx="2290371" cy="328423"/>
+          <a:ext cx="2149306" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5793,7 +5793,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：手前ブロック透過設定ダウン</a:t>
+            <a:t>：手前ブロック透過設定切替</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5821,7 +5821,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1184987" y="267477"/>
+          <a:off x="1187499" y="4254520"/>
           <a:ext cx="456535" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5937,7 +5937,7 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>46653</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2307683" cy="328423"/>
+    <xdr:ext cx="1320233" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="55" name="テキスト ボックス 54">
@@ -5952,7 +5952,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9140292" y="4735884"/>
-          <a:ext cx="2307683" cy="328423"/>
+          <a:ext cx="1320233" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5988,7 +5988,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：手前ブロック透過設定アップ</a:t>
+            <a:t>：ブロック削除</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6262,7 +6262,7 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>83978</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1851982" cy="328423"/>
+    <xdr:ext cx="2225033" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="62" name="テキスト ボックス 61">
@@ -6276,8 +6276,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9116008" y="2883161"/>
-          <a:ext cx="1851982" cy="328423"/>
+          <a:off x="9140292" y="6883363"/>
+          <a:ext cx="2225033" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6317,9 +6317,12 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>ON/OFF</a:t>
+            <a:t>ON/ </a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>範囲操作</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>

--- a/80_Asset/画像リソース/入力設定.xlsx
+++ b/80_Asset/画像リソース/入力設定.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\画像リソース\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151C90C4-48B9-4E36-825D-7DCFE0435E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED2C7C9-FA0D-44F1-BBD2-F831AF27AE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7491" yWindow="4877" windowWidth="24686" windowHeight="13637" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18720" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5691,7 +5691,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1184987" y="1586204"/>
+          <a:off x="1187499" y="5579227"/>
           <a:ext cx="1516634" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5807,7 +5807,7 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>34212</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="456535" cy="328423"/>
+    <xdr:ext cx="1302921" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="52" name="テキスト ボックス 51">
@@ -5822,7 +5822,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1187499" y="4254520"/>
-          <a:ext cx="456535" cy="328423"/>
+          <a:ext cx="1302921" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5858,7 +5858,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：</a:t>
+            <a:t>：範囲選択解除</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6016,7 +6016,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9116008" y="1172548"/>
+          <a:off x="9140292" y="5164376"/>
           <a:ext cx="601831" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6335,7 +6335,7 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>130630</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2304221" cy="564514"/>
+    <xdr:ext cx="2163156" cy="564514"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="63" name="テキスト ボックス 62">
@@ -6349,8 +6349,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9116008" y="3163079"/>
-          <a:ext cx="2304221" cy="564514"/>
+          <a:off x="9140292" y="7164476"/>
+          <a:ext cx="2163156" cy="564514"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6413,7 +6413,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
-            <a:t>：カメラ左右回転</a:t>
+            <a:t>：方位左右切替</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
@@ -11938,7 +11938,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1182735" y="5351696"/>
+          <a:off x="1187499" y="9610119"/>
           <a:ext cx="1516634" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -12263,7 +12263,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9094236" y="4938578"/>
+          <a:off x="9140292" y="9195268"/>
           <a:ext cx="601831" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -18176,7 +18176,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1182735" y="5306651"/>
+          <a:off x="1187499" y="1593381"/>
           <a:ext cx="1516634" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -18501,7 +18501,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9094236" y="4893532"/>
+          <a:off x="9140292" y="1178530"/>
           <a:ext cx="601831" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/80_Asset/画像リソース/入力設定.xlsx
+++ b/80_Asset/画像リソース/入力設定.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\画像リソース\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED2C7C9-FA0D-44F1-BBD2-F831AF27AE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73937F24-6B97-4F67-9256-0D6D06961E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18720" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
   </bookViews>
@@ -6332,10 +6332,10 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>276808</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>130630</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2163156" cy="564514"/>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>80388</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1919756" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="63" name="テキスト ボックス 62">
@@ -6349,8 +6349,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9140292" y="7164476"/>
-          <a:ext cx="2163156" cy="564514"/>
+          <a:off x="9140292" y="7348696"/>
+          <a:ext cx="1919756" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6405,17 +6405,6 @@
             <a:t>縮小</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
-            <a:t>R-Stick Left/Right</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
-            <a:t>：方位左右切替</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11989,7 +11978,7 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>17589</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2290371" cy="328423"/>
+    <xdr:ext cx="2149306" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="208" name="テキスト ボックス 207">
@@ -12004,7 +11993,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1187499" y="8927127"/>
-          <a:ext cx="2290371" cy="328423"/>
+          <a:ext cx="2149306" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12040,7 +12029,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：手前ブロック透過設定ダウン</a:t>
+            <a:t>：手前ブロック透過設定切替</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -12181,75 +12170,10 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>276808</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>91698</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2307683" cy="328423"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="211" name="テキスト ボックス 210">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{612FBF0F-9870-5692-5353-D0F72F3D695E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9140292" y="8766775"/>
-          <a:ext cx="2307683" cy="328423"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>R1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：手前ブロック透過設定アップ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>276808</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>51268</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="601831" cy="328423"/>
+    <xdr:ext cx="1448217" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="212" name="テキスト ボックス 211">
@@ -12264,7 +12188,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9140292" y="9195268"/>
-          <a:ext cx="601831" cy="328423"/>
+          <a:ext cx="1448217" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12300,7 +12224,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：</a:t>
+            <a:t>：メニュー表示</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -12314,7 +12238,7 @@
       <xdr:row>41</xdr:row>
       <xdr:rowOff>11370</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1245341" cy="328423"/>
+    <xdr:ext cx="398955" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="213" name="テキスト ボックス 212">
@@ -12328,8 +12252,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9094236" y="5364138"/>
-          <a:ext cx="1245341" cy="328423"/>
+          <a:off x="9140292" y="9624293"/>
+          <a:ext cx="398955" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12365,7 +12289,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：メニュー表示</a:t>
+            <a:t>：</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -12379,7 +12303,7 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>175676</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="958724" cy="328423"/>
+    <xdr:ext cx="1327223" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="214" name="テキスト ボックス 213">
@@ -12393,8 +12317,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9094236" y="5993903"/>
-          <a:ext cx="958724" cy="328423"/>
+          <a:off x="9140292" y="10023061"/>
+          <a:ext cx="1327223" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12430,7 +12354,15 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：ダッシュ</a:t>
+            <a:t>：攻撃</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>/ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ダッシュ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -12444,7 +12376,7 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>135242</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="407356" cy="328423"/>
+    <xdr:ext cx="1112677" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="215" name="テキスト ボックス 214">
@@ -12458,8 +12390,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9094236" y="6418927"/>
-          <a:ext cx="407356" cy="328423"/>
+          <a:off x="9140292" y="10451550"/>
+          <a:ext cx="1112677" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12495,7 +12427,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：</a:t>
+            <a:t>：アクション</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -12571,10 +12503,10 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>276808</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>175675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2304221" cy="564514"/>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>142180</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1919756" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="217" name="テキスト ボックス 216">
@@ -12588,8 +12520,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9094236" y="6924818"/>
-          <a:ext cx="2304221" cy="564514"/>
+          <a:off x="9140292" y="11396334"/>
+          <a:ext cx="1919756" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12644,17 +12576,6 @@
             <a:t>縮小</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
-            <a:t>R-Stick Left/Right</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
-            <a:t>：カメラ左右回転</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>

--- a/80_Asset/画像リソース/入力設定.xlsx
+++ b/80_Asset/画像リソース/入力設定.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\画像リソース\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73937F24-6B97-4F67-9256-0D6D06961E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A643ED7F-F8EA-4741-B988-3D316724AA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18720" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="18600" xr2:uid="{56C02BF3-3F9F-45BA-920D-22121863796C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17953,7 +17953,7 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>31103</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="696473" cy="328423"/>
+    <xdr:ext cx="1542858" cy="328423"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="310" name="テキスト ボックス 309">
@@ -17967,8 +17967,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1182735" y="3289310"/>
-          <a:ext cx="696473" cy="328423"/>
+          <a:off x="1187499" y="3313565"/>
+          <a:ext cx="1542858" cy="328423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18004,7 +18004,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>：</a:t>
+            <a:t>：カーソル移動</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
